--- a/ge_activation_poc/plan.xlsx
+++ b/ge_activation_poc/plan.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -812,11 +812,78 @@
           <t>saved</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>2026-09-03T23:32:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>D-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>infra</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Region eu + CMEK</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>{"location": "eu", "encryption": "cmek", "cmek_config_id": "default", "kms_key": "projects/PROJECT_ID/locations/europe/keyRings/ge/cryptoKeys/gemini-enterprise"}</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Meets EU data residency (GDPR) | You control the keys; supports third-party connectors</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Region cannot be changed after data stores exist | Key cannot be swapped once applied; all connectors share one CMEK config | First-party connectors use Google-managed keys (except BigQuery/GCS import) | Cloud KMS billed continuously once registered</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Residency + key-control requirements</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://docs.cloud.google.com/gemini/enterprise/docs/cmek</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>google_discovery_engine_cmek_config</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>planning-agent</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>saved</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04T14:59:06Z</t>
         </is>
       </c>
     </row>
